--- a/docs/WishList_Test_Report.xlsx
+++ b/docs/WishList_Test_Report.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Report" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Bugs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality Metrics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Report'!$A$2:$N$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Report'!$A$2:$N$285</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,7 +68,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +100,21 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -117,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -151,6 +168,18 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -516,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N225"/>
+  <dimension ref="A1:N285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -538,7 +567,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Wi$h Li$t – Test Report   |   223 tests   |   April 13, 2026</t>
+          <t>Wi$h Li$t – Test Report   |   283 tests   |   April 13, 2026</t>
         </is>
       </c>
     </row>
@@ -15242,17 +15271,17 @@
       </c>
       <c r="B218" s="7" t="inlineStr">
         <is>
-          <t>test_user_service</t>
+          <t>test_price_observer</t>
         </is>
       </c>
       <c r="C218" s="7" t="inlineStr">
         <is>
-          <t>TestCreateUser</t>
+          <t>TestPriceMonitorAttach</t>
         </is>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>test_calls_repository_save</t>
+          <t>test_attach_adds_observer</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -15262,22 +15291,22 @@
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>Mock repository.save; call service.create_user; assert save called once.</t>
+          <t>Create PriceMonitor; attach MagicMock observer; check _observers list.</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>repository.save called once</t>
+          <t>Observer in monitor._observers</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>repository.save called once</t>
+          <t>Observer in monitor._observers</t>
         </is>
       </c>
       <c r="I218" s="7" t="inlineStr">
         <is>
-          <t>Elif Serra Öncü</t>
+          <t>Akif Emre Reis</t>
         </is>
       </c>
       <c r="J218" s="6" t="inlineStr">
@@ -15310,17 +15339,17 @@
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>test_user_service</t>
+          <t>test_price_observer</t>
         </is>
       </c>
       <c r="C219" s="9" t="inlineStr">
         <is>
-          <t>TestCreateUser</t>
+          <t>TestPriceMonitorAttach</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>test_passes_correct_first_name</t>
+          <t>test_attach_same_observer_twice_is_idempotent</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -15330,22 +15359,22 @@
       </c>
       <c r="F219" s="9" t="inlineStr">
         <is>
-          <t>Call create_user('Zeynep', ...); assert save receives first_name='Zeynep'.</t>
+          <t>Attach same observer twice; check count in _observers.</t>
         </is>
       </c>
       <c r="G219" s="9" t="inlineStr">
         <is>
-          <t>saved_user.first_name == 'Zeynep'</t>
+          <t>_observers.count(obs) == 1</t>
         </is>
       </c>
       <c r="H219" s="9" t="inlineStr">
         <is>
-          <t>saved_user.first_name == 'Zeynep'</t>
+          <t>_observers.count(obs) == 1</t>
         </is>
       </c>
       <c r="I219" s="9" t="inlineStr">
         <is>
-          <t>Elif Serra Öncü</t>
+          <t>Akif Emre Reis</t>
         </is>
       </c>
       <c r="J219" s="8" t="inlineStr">
@@ -15378,17 +15407,17 @@
       </c>
       <c r="B220" s="7" t="inlineStr">
         <is>
-          <t>test_user_service</t>
+          <t>test_price_observer</t>
         </is>
       </c>
       <c r="C220" s="7" t="inlineStr">
         <is>
-          <t>TestCreateUser</t>
+          <t>TestPriceMonitorAttach</t>
         </is>
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
-          <t>test_passes_correct_last_name</t>
+          <t>test_attach_multiple_observers</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -15398,22 +15427,22 @@
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>Call create_user with last_name='Yılmaz'; assert save receives correct last_name.</t>
+          <t>Attach two distinct observers; check len(_observers).</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
-          <t>saved_user.last_name == 'Yılmaz'</t>
+          <t>len(_observers) == 2</t>
         </is>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>saved_user.last_name == 'Yılmaz'</t>
+          <t>len(_observers) == 2</t>
         </is>
       </c>
       <c r="I220" s="7" t="inlineStr">
         <is>
-          <t>Elif Serra Öncü</t>
+          <t>Akif Emre Reis</t>
         </is>
       </c>
       <c r="J220" s="6" t="inlineStr">
@@ -15446,17 +15475,17 @@
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>test_user_service</t>
+          <t>test_price_observer</t>
         </is>
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>TestCreateUser</t>
+          <t>TestPriceMonitorDetach</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>test_passes_correct_email</t>
+          <t>test_detach_removes_observer</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -15466,22 +15495,22 @@
       </c>
       <c r="F221" s="9" t="inlineStr">
         <is>
-          <t>Call create_user with email='can@example.com'; assert save receives same email.</t>
+          <t>Attach then detach observer; check _observers is empty.</t>
         </is>
       </c>
       <c r="G221" s="9" t="inlineStr">
         <is>
-          <t>saved_user.email == 'can@example.com'</t>
+          <t>obs not in _observers</t>
         </is>
       </c>
       <c r="H221" s="9" t="inlineStr">
         <is>
-          <t>saved_user.email == 'can@example.com'</t>
+          <t>obs not in _observers</t>
         </is>
       </c>
       <c r="I221" s="9" t="inlineStr">
         <is>
-          <t>Elif Serra Öncü</t>
+          <t>Akif Emre Reis</t>
         </is>
       </c>
       <c r="J221" s="8" t="inlineStr">
@@ -15514,17 +15543,17 @@
       </c>
       <c r="B222" s="7" t="inlineStr">
         <is>
-          <t>test_user_service</t>
+          <t>test_price_observer</t>
         </is>
       </c>
       <c r="C222" s="7" t="inlineStr">
         <is>
-          <t>TestCreateUser</t>
+          <t>TestPriceMonitorDetach</t>
         </is>
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
-          <t>test_passes_user_create_schema_to_repo</t>
+          <t>test_detach_non_attached_observer_does_not_raise</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -15534,22 +15563,22 @@
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>Call create_user; assert arg passed to save is UserCreate instance.</t>
+          <t>Detach observer that was never attached; expect no exception.</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>isinstance(saved_user, UserCreate) == True</t>
+          <t>No exception raised</t>
         </is>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>isinstance(saved_user, UserCreate) == True</t>
+          <t>No exception raised</t>
         </is>
       </c>
       <c r="I222" s="7" t="inlineStr">
         <is>
-          <t>Elif Serra Öncü</t>
+          <t>Akif Emre Reis</t>
         </is>
       </c>
       <c r="J222" s="6" t="inlineStr">
@@ -15582,17 +15611,17 @@
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>test_user_service</t>
+          <t>test_price_observer</t>
         </is>
       </c>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>TestCreateUser</t>
+          <t>TestPriceMonitorDetach</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>test_returns_saved_user</t>
+          <t>test_detach_only_removes_target_observer</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -15602,22 +15631,22 @@
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>Mock save to return UserRead; assert same object returned from service.</t>
+          <t>Attach obs1 and obs2; detach obs1; verify obs2 still present.</t>
         </is>
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>Returns same object as repository.save</t>
+          <t>obs2 in _observers, obs1 not in _observers</t>
         </is>
       </c>
       <c r="H223" s="9" t="inlineStr">
         <is>
-          <t>Returns same object as repository.save</t>
+          <t>obs2 in _observers, obs1 not in _observers</t>
         </is>
       </c>
       <c r="I223" s="9" t="inlineStr">
         <is>
-          <t>Elif Serra Öncü</t>
+          <t>Akif Emre Reis</t>
         </is>
       </c>
       <c r="J223" s="8" t="inlineStr">
@@ -15650,17 +15679,17 @@
       </c>
       <c r="B224" s="7" t="inlineStr">
         <is>
-          <t>test_user_service</t>
+          <t>test_price_observer</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
         <is>
-          <t>TestCreateUser</t>
+          <t>TestPriceMonitorNotify</t>
         </is>
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
-          <t>test_returns_user_with_id</t>
+          <t>test_notify_calls_update_on_all_observers</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -15670,22 +15699,22 @@
       </c>
       <c r="F224" s="7" t="inlineStr">
         <is>
-          <t>Mock save to return UserRead with UUID id; assert result.id is not None.</t>
+          <t>Attach two observers; call notify; assert update called once on each.</t>
         </is>
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>result.id != None</t>
+          <t>Both observers' update called with (product, old, new)</t>
         </is>
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
-          <t>result.id != None</t>
+          <t>Both observers' update called with (product, old, new)</t>
         </is>
       </c>
       <c r="I224" s="7" t="inlineStr">
         <is>
-          <t>Elif Serra Öncü</t>
+          <t>Akif Emre Reis</t>
         </is>
       </c>
       <c r="J224" s="6" t="inlineStr">
@@ -15718,68 +15747,4148 @@
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C225" s="9" t="inlineStr">
+        <is>
+          <t>TestPriceMonitorNotify</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="inlineStr">
+        <is>
+          <t>test_notify_with_no_observers_does_not_raise</t>
+        </is>
+      </c>
+      <c r="E225" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>Call notify on empty PriceMonitor; expect no exception.</t>
+        </is>
+      </c>
+      <c r="G225" s="9" t="inlineStr">
+        <is>
+          <t>No exception raised</t>
+        </is>
+      </c>
+      <c r="H225" s="9" t="inlineStr">
+        <is>
+          <t>No exception raised</t>
+        </is>
+      </c>
+      <c r="I225" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J225" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K225" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L225" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M225" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L230</t>
+        </is>
+      </c>
+      <c r="N225" s="9" t="inlineStr"/>
+    </row>
+    <row r="226" ht="38" customHeight="1">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>TC-224</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C226" s="7" t="inlineStr">
+        <is>
+          <t>TestPriceMonitorNotify</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>test_notify_passes_correct_old_and_new_price</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>Attach observer; call notify(product, 9999.0, 7500.0); assert update args.</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>old_price==9999.0, new_price==7500.0</t>
+        </is>
+      </c>
+      <c r="H226" s="7" t="inlineStr">
+        <is>
+          <t>old_price==9999.0, new_price==7500.0</t>
+        </is>
+      </c>
+      <c r="I226" s="7" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J226" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K226" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L226" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M226" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L231</t>
+        </is>
+      </c>
+      <c r="N226" s="7" t="inlineStr"/>
+    </row>
+    <row r="227" ht="38" customHeight="1">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>TC-225</t>
+        </is>
+      </c>
+      <c r="B227" s="9" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C227" s="9" t="inlineStr">
+        <is>
+          <t>TestPriceMonitorNotify</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="inlineStr">
+        <is>
+          <t>test_notify_passes_correct_product</t>
+        </is>
+      </c>
+      <c r="E227" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>Attach observer; call notify with product name='Phone'; assert product passed.</t>
+        </is>
+      </c>
+      <c r="G227" s="9" t="inlineStr">
+        <is>
+          <t>called_product['name'] == 'Phone'</t>
+        </is>
+      </c>
+      <c r="H227" s="9" t="inlineStr">
+        <is>
+          <t>called_product['name'] == 'Phone'</t>
+        </is>
+      </c>
+      <c r="I227" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J227" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K227" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L227" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M227" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L232</t>
+        </is>
+      </c>
+      <c r="N227" s="9" t="inlineStr"/>
+    </row>
+    <row r="228" ht="38" customHeight="1">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>TC-226</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C228" s="7" t="inlineStr">
+        <is>
+          <t>TestPriceMonitorInterface</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>test_price_monitor_is_price_subject</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>Check issubclass(PriceMonitor, PriceSubject).</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H228" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I228" s="7" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J228" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K228" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L228" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M228" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L233</t>
+        </is>
+      </c>
+      <c r="N228" s="7" t="inlineStr"/>
+    </row>
+    <row r="229" ht="38" customHeight="1">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>TC-227</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C229" s="9" t="inlineStr">
+        <is>
+          <t>TestPriceMonitorInterface</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="inlineStr">
+        <is>
+          <t>test_new_monitor_has_empty_observer_list</t>
+        </is>
+      </c>
+      <c r="E229" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>Instantiate PriceMonitor; check _observers == [].</t>
+        </is>
+      </c>
+      <c r="G229" s="9" t="inlineStr">
+        <is>
+          <t>_observers == []</t>
+        </is>
+      </c>
+      <c r="H229" s="9" t="inlineStr">
+        <is>
+          <t>_observers == []</t>
+        </is>
+      </c>
+      <c r="I229" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J229" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K229" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L229" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M229" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L234</t>
+        </is>
+      </c>
+      <c r="N229" s="9" t="inlineStr"/>
+    </row>
+    <row r="230" ht="38" customHeight="1">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>TC-228</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverInterface</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>test_is_price_observer</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>Check issubclass(TargetPriceNotificationObserver, PriceObserver).</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H230" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I230" s="7" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J230" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K230" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L230" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M230" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L235</t>
+        </is>
+      </c>
+      <c r="N230" s="7" t="inlineStr"/>
+    </row>
+    <row r="231" ht="38" customHeight="1">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>TC-229</t>
+        </is>
+      </c>
+      <c r="B231" s="9" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverInterface</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>test_update_method_exists</t>
+        </is>
+      </c>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>Instantiate observer; check callable(obs.update).</t>
+        </is>
+      </c>
+      <c r="G231" s="9" t="inlineStr">
+        <is>
+          <t>callable(obs.update) == True</t>
+        </is>
+      </c>
+      <c r="H231" s="9" t="inlineStr">
+        <is>
+          <t>callable(obs.update) == True</t>
+        </is>
+      </c>
+      <c r="I231" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J231" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K231" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L231" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M231" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L236</t>
+        </is>
+      </c>
+      <c r="N231" s="9" t="inlineStr"/>
+    </row>
+    <row r="232" ht="38" customHeight="1">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>TC-230</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C232" s="7" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>test_sends_notification_when_price_drops_to_target</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>Mock supabase; call update with old=5000, new=3999, target=4000; assert insert called.</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="inlineStr">
+        <is>
+          <t>supabase.table.insert called once</t>
+        </is>
+      </c>
+      <c r="H232" s="7" t="inlineStr">
+        <is>
+          <t>supabase.table.insert called once</t>
+        </is>
+      </c>
+      <c r="I232" s="7" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J232" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K232" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L232" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M232" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L237</t>
+        </is>
+      </c>
+      <c r="N232" s="7" t="inlineStr"/>
+    </row>
+    <row r="233" ht="38" customHeight="1">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>TC-231</t>
+        </is>
+      </c>
+      <c r="B233" s="9" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>test_does_not_notify_when_price_above_target</t>
+        </is>
+      </c>
+      <c r="E233" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>Call update with new=4500, target=4000; assert insert NOT called.</t>
+        </is>
+      </c>
+      <c r="G233" s="9" t="inlineStr">
+        <is>
+          <t>insert not called</t>
+        </is>
+      </c>
+      <c r="H233" s="9" t="inlineStr">
+        <is>
+          <t>insert not called</t>
+        </is>
+      </c>
+      <c r="I233" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J233" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K233" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L233" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M233" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L238</t>
+        </is>
+      </c>
+      <c r="N233" s="9" t="inlineStr"/>
+    </row>
+    <row r="234" ht="38" customHeight="1">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>TC-232</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C234" s="7" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>test_does_not_notify_when_target_price_is_none</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>Set product target_price=None; call update; assert insert not called.</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>insert not called</t>
+        </is>
+      </c>
+      <c r="H234" s="7" t="inlineStr">
+        <is>
+          <t>insert not called</t>
+        </is>
+      </c>
+      <c r="I234" s="7" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J234" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K234" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L234" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M234" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L239</t>
+        </is>
+      </c>
+      <c r="N234" s="7" t="inlineStr"/>
+    </row>
+    <row r="235" ht="38" customHeight="1">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>TC-233</t>
+        </is>
+      </c>
+      <c r="B235" s="9" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C235" s="9" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D235" s="9" t="inlineStr">
+        <is>
+          <t>test_does_not_spam_when_old_price_already_below_target</t>
+        </is>
+      </c>
+      <c r="E235" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>Call update with old_price=3500 already below target=4000; assert insert not called.</t>
+        </is>
+      </c>
+      <c r="G235" s="9" t="inlineStr">
+        <is>
+          <t>insert not called</t>
+        </is>
+      </c>
+      <c r="H235" s="9" t="inlineStr">
+        <is>
+          <t>insert not called</t>
+        </is>
+      </c>
+      <c r="I235" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J235" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K235" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L235" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M235" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L240</t>
+        </is>
+      </c>
+      <c r="N235" s="9" t="inlineStr"/>
+    </row>
+    <row r="236" ht="38" customHeight="1">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>TC-234</t>
+        </is>
+      </c>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C236" s="7" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>test_notification_contains_correct_user_id</t>
+        </is>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>Call update; inspect inserted row; assert user_id matches product user_id.</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>inserted['user_id'] == product['user_id']</t>
+        </is>
+      </c>
+      <c r="H236" s="7" t="inlineStr">
+        <is>
+          <t>inserted['user_id'] == product['user_id']</t>
+        </is>
+      </c>
+      <c r="I236" s="7" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J236" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K236" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L236" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M236" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L241</t>
+        </is>
+      </c>
+      <c r="N236" s="7" t="inlineStr"/>
+    </row>
+    <row r="237" ht="38" customHeight="1">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>TC-235</t>
+        </is>
+      </c>
+      <c r="B237" s="9" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="inlineStr">
+        <is>
+          <t>test_notification_contains_correct_product_id</t>
+        </is>
+      </c>
+      <c r="E237" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>Call update; inspect inserted row; assert product_id matches.</t>
+        </is>
+      </c>
+      <c r="G237" s="9" t="inlineStr">
+        <is>
+          <t>inserted['product_id'] == product['id']</t>
+        </is>
+      </c>
+      <c r="H237" s="9" t="inlineStr">
+        <is>
+          <t>inserted['product_id'] == product['id']</t>
+        </is>
+      </c>
+      <c r="I237" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J237" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K237" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L237" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M237" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L242</t>
+        </is>
+      </c>
+      <c r="N237" s="9" t="inlineStr"/>
+    </row>
+    <row r="238" ht="38" customHeight="1">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>TC-236</t>
+        </is>
+      </c>
+      <c r="B238" s="7" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C238" s="7" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>test_notification_is_unread_by_default</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>Call update; inspect inserted row; assert is_read == False.</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>inserted['is_read'] == False</t>
+        </is>
+      </c>
+      <c r="H238" s="7" t="inlineStr">
+        <is>
+          <t>inserted['is_read'] == False</t>
+        </is>
+      </c>
+      <c r="I238" s="7" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J238" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K238" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L238" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M238" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L243</t>
+        </is>
+      </c>
+      <c r="N238" s="7" t="inlineStr"/>
+    </row>
+    <row r="239" ht="38" customHeight="1">
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>TC-237</t>
+        </is>
+      </c>
+      <c r="B239" s="9" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="inlineStr">
+        <is>
+          <t>test_notification_message_contains_product_name</t>
+        </is>
+      </c>
+      <c r="E239" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>Call update with product name='MacBook Pro'; assert 'MacBook Pro' in inserted message.</t>
+        </is>
+      </c>
+      <c r="G239" s="9" t="inlineStr">
+        <is>
+          <t>'MacBook Pro' in inserted['message']</t>
+        </is>
+      </c>
+      <c r="H239" s="9" t="inlineStr">
+        <is>
+          <t>'MacBook Pro' in inserted['message']</t>
+        </is>
+      </c>
+      <c r="I239" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J239" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K239" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L239" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M239" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L244</t>
+        </is>
+      </c>
+      <c r="N239" s="9" t="inlineStr"/>
+    </row>
+    <row r="240" ht="38" customHeight="1">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>TC-238</t>
+        </is>
+      </c>
+      <c r="B240" s="7" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C240" s="7" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D240" s="7" t="inlineStr">
+        <is>
+          <t>test_does_not_raise_when_supabase_fails</t>
+        </is>
+      </c>
+      <c r="E240" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F240" s="7" t="inlineStr">
+        <is>
+          <t>Mock supabase.table to raise Exception; call update; no exception should propagate.</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="inlineStr">
+        <is>
+          <t>No exception raised</t>
+        </is>
+      </c>
+      <c r="H240" s="7" t="inlineStr">
+        <is>
+          <t>No exception raised</t>
+        </is>
+      </c>
+      <c r="I240" s="7" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J240" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K240" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L240" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M240" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L245</t>
+        </is>
+      </c>
+      <c r="N240" s="7" t="inlineStr"/>
+    </row>
+    <row r="241" ht="38" customHeight="1">
+      <c r="A241" s="8" t="inlineStr">
+        <is>
+          <t>TC-239</t>
+        </is>
+      </c>
+      <c r="B241" s="9" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
+        <is>
+          <t>test_notifies_when_old_price_is_none</t>
+        </is>
+      </c>
+      <c r="E241" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>Call update with old_price=None and new_price below target; assert insert called.</t>
+        </is>
+      </c>
+      <c r="G241" s="9" t="inlineStr">
+        <is>
+          <t>insert called once</t>
+        </is>
+      </c>
+      <c r="H241" s="9" t="inlineStr">
+        <is>
+          <t>insert called once</t>
+        </is>
+      </c>
+      <c r="I241" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J241" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K241" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L241" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M241" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L246</t>
+        </is>
+      </c>
+      <c r="N241" s="9" t="inlineStr"/>
+    </row>
+    <row r="242" ht="38" customHeight="1">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>TC-240</t>
+        </is>
+      </c>
+      <c r="B242" s="7" t="inlineStr">
+        <is>
+          <t>test_price_observer</t>
+        </is>
+      </c>
+      <c r="C242" s="7" t="inlineStr">
+        <is>
+          <t>TestTargetPriceNotificationObserverUpdate</t>
+        </is>
+      </c>
+      <c r="D242" s="7" t="inlineStr">
+        <is>
+          <t>test_notifies_exactly_at_target_price</t>
+        </is>
+      </c>
+      <c r="E242" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F242" s="7" t="inlineStr">
+        <is>
+          <t>Call update with new_price == target_price; assert insert called (boundary condition).</t>
+        </is>
+      </c>
+      <c r="G242" s="7" t="inlineStr">
+        <is>
+          <t>insert called once</t>
+        </is>
+      </c>
+      <c r="H242" s="7" t="inlineStr">
+        <is>
+          <t>insert called once</t>
+        </is>
+      </c>
+      <c r="I242" s="7" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J242" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K242" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L242" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M242" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L247</t>
+        </is>
+      </c>
+      <c r="N242" s="7" t="inlineStr"/>
+    </row>
+    <row r="243" ht="38" customHeight="1">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>TC-241</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>TestGetUserNotificationsEndpoint</t>
+        </is>
+      </c>
+      <c r="D243" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_200</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>GET /users/{user_id}/notifications; mock supabase returning []; expect 200.</t>
+        </is>
+      </c>
+      <c r="G243" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="H243" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="I243" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J243" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K243" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L243" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M243" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L248</t>
+        </is>
+      </c>
+      <c r="N243" s="4" t="inlineStr"/>
+    </row>
+    <row r="244" ht="38" customHeight="1">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>TC-242</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>TestGetUserNotificationsEndpoint</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>test_response_is_list</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>GET /users/{id}/notifications; check response body type.</t>
+        </is>
+      </c>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>Response body is JSON array</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="inlineStr">
+        <is>
+          <t>Response body is JSON array</t>
+        </is>
+      </c>
+      <c r="I244" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J244" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K244" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L244" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M244" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L249</t>
+        </is>
+      </c>
+      <c r="N244" s="4" t="inlineStr"/>
+    </row>
+    <row r="245" ht="38" customHeight="1">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>TC-243</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>TestGetUserNotificationsEndpoint</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_notifications_for_user</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>Mock supabase to return 2 notifications; GET endpoint; count items.</t>
+        </is>
+      </c>
+      <c r="G245" s="4" t="inlineStr">
+        <is>
+          <t>len(response) == 2</t>
+        </is>
+      </c>
+      <c r="H245" s="4" t="inlineStr">
+        <is>
+          <t>len(response) == 2</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J245" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L245" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M245" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L250</t>
+        </is>
+      </c>
+      <c r="N245" s="4" t="inlineStr"/>
+    </row>
+    <row r="246" ht="38" customHeight="1">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>TC-244</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>TestGetUserNotificationsEndpoint</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_has_message_field</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>GET notifications; check first item has 'message' key.</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>Response item contains 'message'</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>Response item contains 'message'</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J246" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K246" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L246" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M246" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L251</t>
+        </is>
+      </c>
+      <c r="N246" s="4" t="inlineStr"/>
+    </row>
+    <row r="247" ht="38" customHeight="1">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>TC-245</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>TestGetUserNotificationsEndpoint</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_has_is_read_field</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>GET notifications; check first item has 'is_read' key.</t>
+        </is>
+      </c>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>Response item contains 'is_read'</t>
+        </is>
+      </c>
+      <c r="H247" s="4" t="inlineStr">
+        <is>
+          <t>Response item contains 'is_read'</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J247" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K247" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L247" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M247" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L252</t>
+        </is>
+      </c>
+      <c r="N247" s="4" t="inlineStr"/>
+    </row>
+    <row r="248" ht="38" customHeight="1">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>TC-246</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>TestGetUserNotificationsEndpoint</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_500_on_supabase_error</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>Mock supabase.table to raise Exception; GET notifications.</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J248" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L248" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M248" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L253</t>
+        </is>
+      </c>
+      <c r="N248" s="4" t="inlineStr"/>
+    </row>
+    <row r="249" ht="38" customHeight="1">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>TC-247</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>TestGetUserNotificationsEndpoint</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr">
+        <is>
+          <t>test_invalid_user_id_returns_422</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>GET /users/not-a-uuid/notifications.</t>
+        </is>
+      </c>
+      <c r="G249" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 422 Unprocessable Entity</t>
+        </is>
+      </c>
+      <c r="H249" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 422 Unprocessable Entity</t>
+        </is>
+      </c>
+      <c r="I249" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J249" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K249" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L249" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M249" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L254</t>
+        </is>
+      </c>
+      <c r="N249" s="4" t="inlineStr"/>
+    </row>
+    <row r="250" ht="38" customHeight="1">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>TC-248</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>TestGetUserNotificationsEndpoint</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
+        <is>
+          <t>test_unread_notifications_have_is_read_false</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>Mock unread notification; GET endpoint; assert is_read == False.</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>response[0]['is_read'] == False</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>response[0]['is_read'] == False</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J250" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K250" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L250" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M250" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L255</t>
+        </is>
+      </c>
+      <c r="N250" s="4" t="inlineStr"/>
+    </row>
+    <row r="251" ht="38" customHeight="1">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>TC-249</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkNotificationReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_200_on_success</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>PUT /notifications/{id}/read; mock supabase returning updated notification.</t>
+        </is>
+      </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J251" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K251" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L251" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M251" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L256</t>
+        </is>
+      </c>
+      <c r="N251" s="4" t="inlineStr"/>
+    </row>
+    <row r="252" ht="38" customHeight="1">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>TC-250</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkNotificationReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="inlineStr">
+        <is>
+          <t>test_response_is_read_true</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>PUT mark-read; assert response is_read == True.</t>
+        </is>
+      </c>
+      <c r="G252" s="4" t="inlineStr">
+        <is>
+          <t>response['is_read'] == True</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>response['is_read'] == True</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J252" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K252" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L252" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M252" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L257</t>
+        </is>
+      </c>
+      <c r="N252" s="4" t="inlineStr"/>
+    </row>
+    <row r="253" ht="38" customHeight="1">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>TC-251</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkNotificationReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D253" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_404_when_notification_not_found</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>Mock supabase returning empty data; PUT mark-read.</t>
+        </is>
+      </c>
+      <c r="G253" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 404 Not Found</t>
+        </is>
+      </c>
+      <c r="H253" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 404 Not Found</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J253" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K253" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L253" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M253" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L258</t>
+        </is>
+      </c>
+      <c r="N253" s="4" t="inlineStr"/>
+    </row>
+    <row r="254" ht="38" customHeight="1">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>TC-252</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkNotificationReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_500_on_supabase_error</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>Mock supabase.table to raise Exception; PUT mark-read.</t>
+        </is>
+      </c>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J254" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K254" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L254" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M254" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L259</t>
+        </is>
+      </c>
+      <c r="N254" s="4" t="inlineStr"/>
+    </row>
+    <row r="255" ht="38" customHeight="1">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>TC-253</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkNotificationReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="inlineStr">
+        <is>
+          <t>test_invalid_notification_id_returns_422</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>PUT /notifications/not-a-uuid/read.</t>
+        </is>
+      </c>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 422 Unprocessable Entity</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 422 Unprocessable Entity</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J255" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K255" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L255" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M255" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L260</t>
+        </is>
+      </c>
+      <c r="N255" s="4" t="inlineStr"/>
+    </row>
+    <row r="256" ht="38" customHeight="1">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>TC-254</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkNotificationReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D256" s="4" t="inlineStr">
+        <is>
+          <t>test_updates_is_read_field_in_supabase</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F256" s="4" t="inlineStr">
+        <is>
+          <t>PUT mark-read; assert supabase.update called with {'is_read': True}.</t>
+        </is>
+      </c>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>update called with {'is_read': True}</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>update called with {'is_read': True}</t>
+        </is>
+      </c>
+      <c r="I256" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J256" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K256" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L256" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M256" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L261</t>
+        </is>
+      </c>
+      <c r="N256" s="4" t="inlineStr"/>
+    </row>
+    <row r="257" ht="38" customHeight="1">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>TC-255</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkAllNotificationsReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D257" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_200_on_success</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>PUT /users/{id}/notifications/read; mock supabase; expect 200.</t>
+        </is>
+      </c>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J257" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K257" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L257" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M257" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L262</t>
+        </is>
+      </c>
+      <c r="N257" s="4" t="inlineStr"/>
+    </row>
+    <row r="258" ht="38" customHeight="1">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>TC-256</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkAllNotificationsReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D258" s="4" t="inlineStr">
+        <is>
+          <t>test_response_contains_detail</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>PUT mark-all-read; assert response has 'detail' key.</t>
+        </is>
+      </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>Response has 'detail' key</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="inlineStr">
+        <is>
+          <t>Response has 'detail' key</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J258" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K258" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L258" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M258" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L263</t>
+        </is>
+      </c>
+      <c r="N258" s="4" t="inlineStr"/>
+    </row>
+    <row r="259" ht="38" customHeight="1">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>TC-257</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkAllNotificationsReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D259" s="4" t="inlineStr">
+        <is>
+          <t>test_calls_update_with_is_read_true</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>PUT mark-all-read; assert supabase.update called with {'is_read': True}.</t>
+        </is>
+      </c>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>update called with {'is_read': True}</t>
+        </is>
+      </c>
+      <c r="H259" s="4" t="inlineStr">
+        <is>
+          <t>update called with {'is_read': True}</t>
+        </is>
+      </c>
+      <c r="I259" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J259" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K259" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L259" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M259" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L264</t>
+        </is>
+      </c>
+      <c r="N259" s="4" t="inlineStr"/>
+    </row>
+    <row r="260" ht="38" customHeight="1">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>TC-258</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkAllNotificationsReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D260" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_500_on_supabase_error</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F260" s="4" t="inlineStr">
+        <is>
+          <t>Mock supabase.table to raise Exception; PUT mark-all-read.</t>
+        </is>
+      </c>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="I260" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J260" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K260" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L260" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M260" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L265</t>
+        </is>
+      </c>
+      <c r="N260" s="4" t="inlineStr"/>
+    </row>
+    <row r="261" ht="38" customHeight="1">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>TC-259</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>test_notification_api</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>TestMarkAllNotificationsReadEndpoint</t>
+        </is>
+      </c>
+      <c r="D261" s="4" t="inlineStr">
+        <is>
+          <t>test_invalid_user_id_returns_422</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>PUT /users/not-a-uuid/notifications/read.</t>
+        </is>
+      </c>
+      <c r="G261" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 422 Unprocessable Entity</t>
+        </is>
+      </c>
+      <c r="H261" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 422 Unprocessable Entity</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J261" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K261" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L261" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M261" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L266</t>
+        </is>
+      </c>
+      <c r="N261" s="4" t="inlineStr"/>
+    </row>
+    <row r="262" ht="38" customHeight="1">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>TC-260</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>TestGetPriceHistoryEndpoint</t>
+        </is>
+      </c>
+      <c r="D262" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_200</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F262" s="4" t="inlineStr">
+        <is>
+          <t>GET /products/{id}/price-history; mock supabase returning []; expect 200.</t>
+        </is>
+      </c>
+      <c r="G262" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="I262" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J262" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K262" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L262" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M262" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L267</t>
+        </is>
+      </c>
+      <c r="N262" s="4" t="inlineStr"/>
+    </row>
+    <row r="263" ht="38" customHeight="1">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>TC-261</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>TestGetPriceHistoryEndpoint</t>
+        </is>
+      </c>
+      <c r="D263" s="4" t="inlineStr">
+        <is>
+          <t>test_response_is_list</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>GET price-history; assert response body is JSON array.</t>
+        </is>
+      </c>
+      <c r="G263" s="4" t="inlineStr">
+        <is>
+          <t>Response is list</t>
+        </is>
+      </c>
+      <c r="H263" s="4" t="inlineStr">
+        <is>
+          <t>Response is list</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J263" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K263" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L263" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M263" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L268</t>
+        </is>
+      </c>
+      <c r="N263" s="4" t="inlineStr"/>
+    </row>
+    <row r="264" ht="38" customHeight="1">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>TC-262</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>TestGetPriceHistoryEndpoint</t>
+        </is>
+      </c>
+      <c r="D264" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_correct_number_of_records</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>Mock 4 price records; GET price-history; count items.</t>
+        </is>
+      </c>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>len(response) == 4</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>len(response) == 4</t>
+        </is>
+      </c>
+      <c r="I264" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J264" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K264" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L264" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M264" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L269</t>
+        </is>
+      </c>
+      <c r="N264" s="4" t="inlineStr"/>
+    </row>
+    <row r="265" ht="38" customHeight="1">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>TC-263</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>TestGetPriceHistoryEndpoint</t>
+        </is>
+      </c>
+      <c r="D265" s="4" t="inlineStr">
+        <is>
+          <t>test_record_contains_price_field</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>GET price-history; check first record has 'price' key.</t>
+        </is>
+      </c>
+      <c r="G265" s="4" t="inlineStr">
+        <is>
+          <t>Response item contains 'price'</t>
+        </is>
+      </c>
+      <c r="H265" s="4" t="inlineStr">
+        <is>
+          <t>Response item contains 'price'</t>
+        </is>
+      </c>
+      <c r="I265" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J265" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K265" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L265" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M265" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L270</t>
+        </is>
+      </c>
+      <c r="N265" s="4" t="inlineStr"/>
+    </row>
+    <row r="266" ht="38" customHeight="1">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>TC-264</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>TestGetPriceHistoryEndpoint</t>
+        </is>
+      </c>
+      <c r="D266" s="4" t="inlineStr">
+        <is>
+          <t>test_record_contains_checked_at_field</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>GET price-history; check first record has 'checked_at' key.</t>
+        </is>
+      </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>Response item contains 'checked_at'</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>Response item contains 'checked_at'</t>
+        </is>
+      </c>
+      <c r="I266" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J266" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K266" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L266" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M266" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L271</t>
+        </is>
+      </c>
+      <c r="N266" s="4" t="inlineStr"/>
+    </row>
+    <row r="267" ht="38" customHeight="1">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>TC-265</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>TestGetPriceHistoryEndpoint</t>
+        </is>
+      </c>
+      <c r="D267" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_empty_list_when_no_history</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>Mock empty data; GET price-history; assert response == [].</t>
+        </is>
+      </c>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>response == []</t>
+        </is>
+      </c>
+      <c r="H267" s="4" t="inlineStr">
+        <is>
+          <t>response == []</t>
+        </is>
+      </c>
+      <c r="I267" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J267" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L267" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M267" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L272</t>
+        </is>
+      </c>
+      <c r="N267" s="4" t="inlineStr"/>
+    </row>
+    <row r="268" ht="38" customHeight="1">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>TC-266</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>TestGetPriceHistoryEndpoint</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="inlineStr">
+        <is>
+          <t>test_invalid_product_id_returns_422</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F268" s="4" t="inlineStr">
+        <is>
+          <t>GET /products/not-a-uuid/price-history.</t>
+        </is>
+      </c>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 422 Unprocessable Entity</t>
+        </is>
+      </c>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 422 Unprocessable Entity</t>
+        </is>
+      </c>
+      <c r="I268" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J268" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K268" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L268" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M268" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L273</t>
+        </is>
+      </c>
+      <c r="N268" s="4" t="inlineStr"/>
+    </row>
+    <row r="269" ht="38" customHeight="1">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>TC-267</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>TestGetPriceHistoryEndpoint</t>
+        </is>
+      </c>
+      <c r="D269" s="4" t="inlineStr">
+        <is>
+          <t>test_price_values_are_numeric</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>Mock price=2999.99; GET price-history; assert isinstance(price, (int, float)).</t>
+        </is>
+      </c>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>price is numeric</t>
+        </is>
+      </c>
+      <c r="H269" s="4" t="inlineStr">
+        <is>
+          <t>price is numeric</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J269" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K269" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L269" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M269" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L274</t>
+        </is>
+      </c>
+      <c r="N269" s="4" t="inlineStr"/>
+    </row>
+    <row r="270" ht="38" customHeight="1">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>TC-268</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>TestSupportedPlatformsEndpoint</t>
+        </is>
+      </c>
+      <c r="D270" s="4" t="inlineStr">
+        <is>
+          <t>test_returns_200</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F270" s="4" t="inlineStr">
+        <is>
+          <t>GET /supported-platforms; expect 200.</t>
+        </is>
+      </c>
+      <c r="G270" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J270" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L270" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M270" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L275</t>
+        </is>
+      </c>
+      <c r="N270" s="4" t="inlineStr"/>
+    </row>
+    <row r="271" ht="38" customHeight="1">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>TC-269</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>TestSupportedPlatformsEndpoint</t>
+        </is>
+      </c>
+      <c r="D271" s="4" t="inlineStr">
+        <is>
+          <t>test_response_contains_platforms_key</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>GET /supported-platforms; assert 'platforms' key in response.</t>
+        </is>
+      </c>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>Response has 'platforms' key</t>
+        </is>
+      </c>
+      <c r="H271" s="4" t="inlineStr">
+        <is>
+          <t>Response has 'platforms' key</t>
+        </is>
+      </c>
+      <c r="I271" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J271" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K271" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L271" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M271" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L276</t>
+        </is>
+      </c>
+      <c r="N271" s="4" t="inlineStr"/>
+    </row>
+    <row r="272" ht="38" customHeight="1">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>TC-270</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>TestSupportedPlatformsEndpoint</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="inlineStr">
+        <is>
+          <t>test_platforms_is_list</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>GET /supported-platforms; assert platforms value is list.</t>
+        </is>
+      </c>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>platforms is list</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>platforms is list</t>
+        </is>
+      </c>
+      <c r="I272" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J272" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K272" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L272" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M272" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L277</t>
+        </is>
+      </c>
+      <c r="N272" s="4" t="inlineStr"/>
+    </row>
+    <row r="273" ht="38" customHeight="1">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>TC-271</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>TestSupportedPlatformsEndpoint</t>
+        </is>
+      </c>
+      <c r="D273" s="4" t="inlineStr">
+        <is>
+          <t>test_platforms_list_is_not_empty</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>GET /supported-platforms; assert len(platforms) &gt; 0.</t>
+        </is>
+      </c>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>len(platforms) &gt; 0</t>
+        </is>
+      </c>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>len(platforms) &gt; 0</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J273" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K273" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L273" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M273" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L278</t>
+        </is>
+      </c>
+      <c r="N273" s="4" t="inlineStr"/>
+    </row>
+    <row r="274" ht="38" customHeight="1">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>TC-272</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>TestSupportedPlatformsEndpoint</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr">
+        <is>
+          <t>test_hepsiburada_in_platforms</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>GET /supported-platforms; assert 'hepsiburada' in any platform string.</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>'hepsiburada' found in platforms</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>'hepsiburada' found in platforms</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J274" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K274" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L274" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M274" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L279</t>
+        </is>
+      </c>
+      <c r="N274" s="4" t="inlineStr"/>
+    </row>
+    <row r="275" ht="38" customHeight="1">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>TC-273</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>TestSupportedPlatformsEndpoint</t>
+        </is>
+      </c>
+      <c r="D275" s="4" t="inlineStr">
+        <is>
+          <t>test_trendyol_in_platforms</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>GET /supported-platforms; assert 'trendyol' in any platform string.</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>'trendyol' found in platforms</t>
+        </is>
+      </c>
+      <c r="H275" s="4" t="inlineStr">
+        <is>
+          <t>'trendyol' found in platforms</t>
+        </is>
+      </c>
+      <c r="I275" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J275" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K275" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L275" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M275" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L280</t>
+        </is>
+      </c>
+      <c r="N275" s="4" t="inlineStr"/>
+    </row>
+    <row r="276" ht="38" customHeight="1">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>TC-274</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>TestSupportedPlatformsEndpoint</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="inlineStr">
+        <is>
+          <t>test_amazon_in_platforms</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>GET /supported-platforms; assert 'amazon' in any platform string.</t>
+        </is>
+      </c>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>'amazon' found in platforms</t>
+        </is>
+      </c>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>'amazon' found in platforms</t>
+        </is>
+      </c>
+      <c r="I276" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J276" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K276" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L276" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M276" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L281</t>
+        </is>
+      </c>
+      <c r="N276" s="4" t="inlineStr"/>
+    </row>
+    <row r="277" ht="38" customHeight="1">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>TC-275</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>TestSupportedPlatformsEndpoint</t>
+        </is>
+      </c>
+      <c r="D277" s="4" t="inlineStr">
+        <is>
+          <t>test_platforms_are_strings</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>GET /supported-platforms; assert all items in platforms are str.</t>
+        </is>
+      </c>
+      <c r="G277" s="4" t="inlineStr">
+        <is>
+          <t>All platform entries are strings</t>
+        </is>
+      </c>
+      <c r="H277" s="4" t="inlineStr">
+        <is>
+          <t>All platform entries are strings</t>
+        </is>
+      </c>
+      <c r="I277" s="4" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="J277" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K277" s="4" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L277" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M277" s="4" t="inlineStr">
+        <is>
+          <t>test_report.txt L282</t>
+        </is>
+      </c>
+      <c r="N277" s="4" t="inlineStr"/>
+    </row>
+    <row r="278" ht="38" customHeight="1">
+      <c r="A278" s="6" t="inlineStr">
+        <is>
+          <t>TC-276</t>
+        </is>
+      </c>
+      <c r="B278" s="7" t="inlineStr">
+        <is>
           <t>test_user_service</t>
         </is>
       </c>
-      <c r="C225" s="9" t="inlineStr">
+      <c r="C278" s="7" t="inlineStr">
         <is>
           <t>TestCreateUser</t>
         </is>
       </c>
-      <c r="D225" s="9" t="inlineStr">
+      <c r="D278" s="7" t="inlineStr">
+        <is>
+          <t>test_calls_repository_save</t>
+        </is>
+      </c>
+      <c r="E278" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F278" s="7" t="inlineStr">
+        <is>
+          <t>Mock repository.save; call service.create_user; assert save called once.</t>
+        </is>
+      </c>
+      <c r="G278" s="7" t="inlineStr">
+        <is>
+          <t>repository.save called once</t>
+        </is>
+      </c>
+      <c r="H278" s="7" t="inlineStr">
+        <is>
+          <t>repository.save called once</t>
+        </is>
+      </c>
+      <c r="I278" s="7" t="inlineStr">
+        <is>
+          <t>Elif Serra Öncü</t>
+        </is>
+      </c>
+      <c r="J278" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K278" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L278" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M278" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L283</t>
+        </is>
+      </c>
+      <c r="N278" s="7" t="inlineStr"/>
+    </row>
+    <row r="279" ht="38" customHeight="1">
+      <c r="A279" s="8" t="inlineStr">
+        <is>
+          <t>TC-277</t>
+        </is>
+      </c>
+      <c r="B279" s="9" t="inlineStr">
+        <is>
+          <t>test_user_service</t>
+        </is>
+      </c>
+      <c r="C279" s="9" t="inlineStr">
+        <is>
+          <t>TestCreateUser</t>
+        </is>
+      </c>
+      <c r="D279" s="9" t="inlineStr">
+        <is>
+          <t>test_passes_correct_first_name</t>
+        </is>
+      </c>
+      <c r="E279" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F279" s="9" t="inlineStr">
+        <is>
+          <t>Call create_user('Zeynep', ...); assert save receives first_name='Zeynep'.</t>
+        </is>
+      </c>
+      <c r="G279" s="9" t="inlineStr">
+        <is>
+          <t>saved_user.first_name == 'Zeynep'</t>
+        </is>
+      </c>
+      <c r="H279" s="9" t="inlineStr">
+        <is>
+          <t>saved_user.first_name == 'Zeynep'</t>
+        </is>
+      </c>
+      <c r="I279" s="9" t="inlineStr">
+        <is>
+          <t>Elif Serra Öncü</t>
+        </is>
+      </c>
+      <c r="J279" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K279" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L279" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M279" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L284</t>
+        </is>
+      </c>
+      <c r="N279" s="9" t="inlineStr"/>
+    </row>
+    <row r="280" ht="38" customHeight="1">
+      <c r="A280" s="6" t="inlineStr">
+        <is>
+          <t>TC-278</t>
+        </is>
+      </c>
+      <c r="B280" s="7" t="inlineStr">
+        <is>
+          <t>test_user_service</t>
+        </is>
+      </c>
+      <c r="C280" s="7" t="inlineStr">
+        <is>
+          <t>TestCreateUser</t>
+        </is>
+      </c>
+      <c r="D280" s="7" t="inlineStr">
+        <is>
+          <t>test_passes_correct_last_name</t>
+        </is>
+      </c>
+      <c r="E280" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F280" s="7" t="inlineStr">
+        <is>
+          <t>Call create_user with last_name='Yılmaz'; assert save receives correct last_name.</t>
+        </is>
+      </c>
+      <c r="G280" s="7" t="inlineStr">
+        <is>
+          <t>saved_user.last_name == 'Yılmaz'</t>
+        </is>
+      </c>
+      <c r="H280" s="7" t="inlineStr">
+        <is>
+          <t>saved_user.last_name == 'Yılmaz'</t>
+        </is>
+      </c>
+      <c r="I280" s="7" t="inlineStr">
+        <is>
+          <t>Elif Serra Öncü</t>
+        </is>
+      </c>
+      <c r="J280" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K280" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L280" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M280" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L285</t>
+        </is>
+      </c>
+      <c r="N280" s="7" t="inlineStr"/>
+    </row>
+    <row r="281" ht="38" customHeight="1">
+      <c r="A281" s="8" t="inlineStr">
+        <is>
+          <t>TC-279</t>
+        </is>
+      </c>
+      <c r="B281" s="9" t="inlineStr">
+        <is>
+          <t>test_user_service</t>
+        </is>
+      </c>
+      <c r="C281" s="9" t="inlineStr">
+        <is>
+          <t>TestCreateUser</t>
+        </is>
+      </c>
+      <c r="D281" s="9" t="inlineStr">
+        <is>
+          <t>test_passes_correct_email</t>
+        </is>
+      </c>
+      <c r="E281" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F281" s="9" t="inlineStr">
+        <is>
+          <t>Call create_user with email='can@example.com'; assert save receives same email.</t>
+        </is>
+      </c>
+      <c r="G281" s="9" t="inlineStr">
+        <is>
+          <t>saved_user.email == 'can@example.com'</t>
+        </is>
+      </c>
+      <c r="H281" s="9" t="inlineStr">
+        <is>
+          <t>saved_user.email == 'can@example.com'</t>
+        </is>
+      </c>
+      <c r="I281" s="9" t="inlineStr">
+        <is>
+          <t>Elif Serra Öncü</t>
+        </is>
+      </c>
+      <c r="J281" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K281" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L281" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M281" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L286</t>
+        </is>
+      </c>
+      <c r="N281" s="9" t="inlineStr"/>
+    </row>
+    <row r="282" ht="38" customHeight="1">
+      <c r="A282" s="6" t="inlineStr">
+        <is>
+          <t>TC-280</t>
+        </is>
+      </c>
+      <c r="B282" s="7" t="inlineStr">
+        <is>
+          <t>test_user_service</t>
+        </is>
+      </c>
+      <c r="C282" s="7" t="inlineStr">
+        <is>
+          <t>TestCreateUser</t>
+        </is>
+      </c>
+      <c r="D282" s="7" t="inlineStr">
+        <is>
+          <t>test_passes_user_create_schema_to_repo</t>
+        </is>
+      </c>
+      <c r="E282" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F282" s="7" t="inlineStr">
+        <is>
+          <t>Call create_user; assert arg passed to save is UserCreate instance.</t>
+        </is>
+      </c>
+      <c r="G282" s="7" t="inlineStr">
+        <is>
+          <t>isinstance(saved_user, UserCreate) == True</t>
+        </is>
+      </c>
+      <c r="H282" s="7" t="inlineStr">
+        <is>
+          <t>isinstance(saved_user, UserCreate) == True</t>
+        </is>
+      </c>
+      <c r="I282" s="7" t="inlineStr">
+        <is>
+          <t>Elif Serra Öncü</t>
+        </is>
+      </c>
+      <c r="J282" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K282" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L282" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M282" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L287</t>
+        </is>
+      </c>
+      <c r="N282" s="7" t="inlineStr"/>
+    </row>
+    <row r="283" ht="38" customHeight="1">
+      <c r="A283" s="8" t="inlineStr">
+        <is>
+          <t>TC-281</t>
+        </is>
+      </c>
+      <c r="B283" s="9" t="inlineStr">
+        <is>
+          <t>test_user_service</t>
+        </is>
+      </c>
+      <c r="C283" s="9" t="inlineStr">
+        <is>
+          <t>TestCreateUser</t>
+        </is>
+      </c>
+      <c r="D283" s="9" t="inlineStr">
+        <is>
+          <t>test_returns_saved_user</t>
+        </is>
+      </c>
+      <c r="E283" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F283" s="9" t="inlineStr">
+        <is>
+          <t>Mock save to return UserRead; assert same object returned from service.</t>
+        </is>
+      </c>
+      <c r="G283" s="9" t="inlineStr">
+        <is>
+          <t>Returns same object as repository.save</t>
+        </is>
+      </c>
+      <c r="H283" s="9" t="inlineStr">
+        <is>
+          <t>Returns same object as repository.save</t>
+        </is>
+      </c>
+      <c r="I283" s="9" t="inlineStr">
+        <is>
+          <t>Elif Serra Öncü</t>
+        </is>
+      </c>
+      <c r="J283" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K283" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L283" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M283" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L288</t>
+        </is>
+      </c>
+      <c r="N283" s="9" t="inlineStr"/>
+    </row>
+    <row r="284" ht="38" customHeight="1">
+      <c r="A284" s="6" t="inlineStr">
+        <is>
+          <t>TC-282</t>
+        </is>
+      </c>
+      <c r="B284" s="7" t="inlineStr">
+        <is>
+          <t>test_user_service</t>
+        </is>
+      </c>
+      <c r="C284" s="7" t="inlineStr">
+        <is>
+          <t>TestCreateUser</t>
+        </is>
+      </c>
+      <c r="D284" s="7" t="inlineStr">
+        <is>
+          <t>test_returns_user_with_id</t>
+        </is>
+      </c>
+      <c r="E284" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F284" s="7" t="inlineStr">
+        <is>
+          <t>Mock save to return UserRead with UUID id; assert result.id is not None.</t>
+        </is>
+      </c>
+      <c r="G284" s="7" t="inlineStr">
+        <is>
+          <t>result.id != None</t>
+        </is>
+      </c>
+      <c r="H284" s="7" t="inlineStr">
+        <is>
+          <t>result.id != None</t>
+        </is>
+      </c>
+      <c r="I284" s="7" t="inlineStr">
+        <is>
+          <t>Elif Serra Öncü</t>
+        </is>
+      </c>
+      <c r="J284" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K284" s="7" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L284" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M284" s="7" t="inlineStr">
+        <is>
+          <t>test_report.txt L289</t>
+        </is>
+      </c>
+      <c r="N284" s="7" t="inlineStr"/>
+    </row>
+    <row r="285" ht="38" customHeight="1">
+      <c r="A285" s="8" t="inlineStr">
+        <is>
+          <t>TC-283</t>
+        </is>
+      </c>
+      <c r="B285" s="9" t="inlineStr">
+        <is>
+          <t>test_user_service</t>
+        </is>
+      </c>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>TestCreateUser</t>
+        </is>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
         <is>
           <t>test_different_emails_produce_different_save_calls</t>
         </is>
       </c>
-      <c r="E225" s="8" t="inlineStr">
+      <c r="E285" s="8" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F225" s="9" t="inlineStr">
+      <c r="F285" s="9" t="inlineStr">
         <is>
           <t>Call create_user twice with different emails; assert save called twice with different emails.</t>
         </is>
       </c>
-      <c r="G225" s="9" t="inlineStr">
+      <c r="G285" s="9" t="inlineStr">
         <is>
           <t>save called 2 times with distinct emails</t>
         </is>
       </c>
-      <c r="H225" s="9" t="inlineStr">
+      <c r="H285" s="9" t="inlineStr">
         <is>
           <t>save called 2 times with distinct emails</t>
         </is>
       </c>
-      <c r="I225" s="9" t="inlineStr">
+      <c r="I285" s="9" t="inlineStr">
         <is>
           <t>Elif Serra Öncü</t>
         </is>
       </c>
-      <c r="J225" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="K225" s="9" t="inlineStr">
-        <is>
-          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
-        </is>
-      </c>
-      <c r="L225" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="M225" s="9" t="inlineStr">
-        <is>
-          <t>test_report.txt L230</t>
-        </is>
-      </c>
-      <c r="N225" s="9" t="inlineStr"/>
+      <c r="J285" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K285" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.13.5 | pytest 9.0.3 | FastAPI | Windows 11</t>
+        </is>
+      </c>
+      <c r="L285" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M285" s="9" t="inlineStr">
+        <is>
+          <t>test_report.txt L290</t>
+        </is>
+      </c>
+      <c r="N285" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N225"/>
+  <autoFilter ref="A2:N285"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -15793,11 +19902,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -15848,43 +19957,45 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="11" t="inlineStr"/>
-      <c r="B6" s="12" t="inlineStr"/>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Test Configuration</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Windows 11 Home, miniconda3, SQLite mock via unittest.mock</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Total Tests</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>223</v>
-      </c>
+      <c r="A7" s="11" t="inlineStr"/>
+      <c r="B7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Total Tests</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>223</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -15892,78 +20003,100 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="11" t="inlineStr"/>
-      <c r="B11" s="12" t="inlineStr"/>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
+          <t>Pass Rate</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="11" t="inlineStr"/>
+      <c r="B13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
           <t>Unit Tests</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>API / Integration Tests</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="11" t="inlineStr"/>
-      <c r="B14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="n">
+        <v>187</v>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Testers</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr"/>
+          <t>API / Integration Tests</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Akif Emre Reis</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>56</v>
-      </c>
+      <c r="A16" s="11" t="inlineStr"/>
+      <c r="B16" s="12" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Alaaddin Gürsoy</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>58</v>
-      </c>
+          <t>Testers</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Elif Serra Öncü</t>
+          <t xml:space="preserve">  Akif Emre Reis</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>60</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Alaaddin Gürsoy</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Elif Serra Öncü</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Gizem Elif Bayar</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B21" s="12" t="n">
         <v>49</v>
       </c>
     </row>
@@ -15973,4 +20106,674 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Bug ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Fix Applied</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Related Test</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Date Fixed</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Fixed By</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>BUG-001</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Scheduler</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>test_scheduler.py tests failing after check_frequency logic was added to scheduler — price_history table not mocked</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Updated setup_supabase_products helper to use table_side_effect distinguishing 'products' vs 'price_history' tables</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>test_scheduler.py (4 tests)</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>BUG-002</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Notification API</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>GET /users/{id}/notifications, PUT /notifications/{id}/read, PUT /users/{id}/notifications/read endpoints had no test coverage — bugs could go undetected</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Added test_notification_api.py with 19 test cases covering all three endpoints</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>test_notification_api.py</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>BUG-003</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Observer Pattern</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>PriceMonitor and TargetPriceNotificationObserver had no unit tests — notification spam prevention logic and supabase error handling untested</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Added test_price_observer.py with 25 test cases covering attach/detach/notify and notification trigger conditions</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>test_price_observer.py</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>BUG-004</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Product API</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>GET /products/{id}/price-history and GET /supported-platforms endpoints had no test coverage</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Added test_product_extra_api.py with 16 test cases</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>test_product_extra_api.py</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Akif Emre Reis</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>BUG-005</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Scraper — Trendyol</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Price extraction failed on pages where discount span was absent; no fallback handled</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Added None-return branch in _extract_price; covered by test_extract_price_returns_none_when_missing</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>test_new_scrapers.py::TestTrendyolScraperParsers</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Alaaddin Gürsoy</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>BUG-006</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Scraper — Boyner</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Image extraction returned data:image base64 placeholder instead of real CDN URL</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Added data-URI skip logic in _extract_image; covered by test_extract_image_skips_data_urls</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>test_new_scrapers.py::TestBoynerScraperParsers</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Gizem Elif Bayar</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>BUG-007</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Category API</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>list-categories endpoint called initialize_default_categories even when categories existed</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Added len check before calling initializer; covered by test_does_not_initialize_when_categories_exist</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>test_category_api.py::TestListCategoriesEndpoint</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Elif Serra Öncü</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Quality Factor</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Quality Criterion</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Target Value</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Related Tests</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Related Requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>All automated tests pass consistently without flaky failures</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Test pass rate</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>100% (283/283)</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>All 283 tests in tests/ directory</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>FR-01 through FR-12 (core functional requirements)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Correctness</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>API endpoints return correct HTTP status codes for valid and invalid inputs</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>HTTP status code accuracy</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>200/422/404/500/502 as specified</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>test_category_api, test_product_api, test_user_api, test_notification_api, test_product_extra_api</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>FR-03 (add product), FR-05 (manage categories), FR-09 (notifications)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>System handles errors gracefully without crashing (DB failures, scraping errors)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Error handling coverage</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>All error paths tested</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>test_scheduler::test_does_not_raise_when_supabase_fails, test_price_observer::test_does_not_raise_when_supabase_fails, test_product_api::test_service_exception_returns_500</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>NFR-02 (fault tolerance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Invalid inputs (non-UUID IDs, missing fields) are rejected with 422</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Input validation coverage</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>100% of UUID params validated</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>test_*::test_invalid_*_returns_422 (28 tests across all modules)</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>NFR-04 (input validation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Design patterns (Factory, Strategy, Observer) are unit-tested independently</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Pattern test coverage</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>3/3 design patterns tested</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>test_scraper_factory (ScraperFactory+Strategy), test_category_factory (Factory), test_price_observer (Observer)</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>SD-01 (Factory pattern), SD-02 (Strategy pattern), SD-03 (Observer pattern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Functionality — Price Tracking</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Scheduler correctly checks prices and triggers notifications at target price</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Price check &amp; notification logic coverage</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>10 scheduler tests + 11 observer tests</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>test_scheduler (10 tests), test_price_observer::TestTargetPriceNotificationObserverUpdate (11 tests)</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>FR-07 (price monitoring), FR-08 (price drop notification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Functionality — Scraping</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Scraper factory routes to correct scraper; all 6 platforms + LLM fallback covered</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Platform coverage</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>6 platforms + LLM fallback = 7 scrapers</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>test_scraper_factory (14 tests), test_new_scrapers (36 tests), test_hepsiburada_scraper (20 tests), test_llm_scraper (16 tests)</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>FR-02 (URL scraping), FR-04 (multi-platform support)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Notification endpoints return correct structure (message, is_read, timestamps)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Response schema correctness</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>All required fields present</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>test_notification_api::test_notification_has_message_field, test_notification_has_is_read_field</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>FR-09 (notification display)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>